--- a/Result/profitability/8034.xlsx
+++ b/Result/profitability/8034.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.04</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2825</v>
+        <v>0.29875</v>
       </c>
       <c r="N2" t="n">
-        <v>48.44</v>
+        <v>49.3475</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.09</v>
       </c>
       <c r="M3" t="n">
-        <v>0.28</v>
+        <v>0.225</v>
       </c>
       <c r="N3" t="n">
-        <v>48.8025</v>
+        <v>49.71125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,16 +899,16 @@
         <v>0.15</v>
       </c>
       <c r="M4" t="n">
-        <v>0.21375</v>
+        <v>0.24375</v>
       </c>
       <c r="N4" t="n">
-        <v>48.765</v>
+        <v>45.23875</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -923,7 +923,7 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" t="n">
         <v>97.3</v>
@@ -1018,10 +1018,10 @@
         <v>0.15</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2325</v>
+        <v>0.2</v>
       </c>
       <c r="N5" t="n">
-        <v>43.29125</v>
+        <v>44.24375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.22</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1425</v>
+        <v>0.09875000000000002</v>
       </c>
       <c r="N6" t="n">
-        <v>41.0475</v>
+        <v>42.0575</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.25</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0375</v>
+        <v>0.02625</v>
       </c>
       <c r="N7" t="n">
-        <v>39.6575</v>
+        <v>40.73125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.31</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0425</v>
+        <v>-0.01375</v>
       </c>
       <c r="N8" t="n">
-        <v>37.4025</v>
+        <v>37.12</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8034</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>76</v>
+      </c>
+      <c r="D75" t="n">
+        <v>37</v>
+      </c>
+      <c r="E75" t="n">
+        <v>39</v>
+      </c>
+      <c r="F75" t="n">
+        <v>51.31</v>
+      </c>
+      <c r="G75" t="n">
+        <v>10</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>12.88%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>3</v>
+      </c>
+      <c r="J75" t="n">
+        <v>13</v>
+      </c>
+      <c r="K75" t="n">
+        <v>13</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.3075</v>
+      </c>
+      <c r="N75" t="n">
+        <v>50.26624999999999</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="X75" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-2.259999999999998</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.04218779167444464</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.52</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>7.620000000000005</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1744106202792401</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
